--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_desktop_grid_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_desktop_grid_pref.xlsx
@@ -467,16 +467,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
         <v>9</v>
       </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -492,13 +492,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -517,7 +517,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -536,7 +536,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -558,16 +558,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
